--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3F4648-3AB5-934D-BB31-B9DCB32894E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2D4A20-7469-834C-BD41-967027CC3C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,12 @@
   </si>
   <si>
     <t>Solved Some two pointer Questions.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Rested due to sickness.</t>
   </si>
 </sst>
 </file>
@@ -2248,27 +2254,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14" t="str">
+    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="12">
+        <v>46271</v>
+      </c>
+      <c r="B31" s="13">
+        <v>300</v>
+      </c>
+      <c r="C31" s="13">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
+        <v>0</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
+        <v>200</v>
+      </c>
+      <c r="I31" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="14" t="str">
+        <v>500</v>
+      </c>
+      <c r="J31" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="16"/>
+        <v>940</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2D4A20-7469-834C-BD41-967027CC3C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D00F7AD-CA3F-CA4B-B426-8E9392C99361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Rested due to sickness.</t>
+  </si>
+  <si>
+    <t>CA of CAP7001</t>
   </si>
 </sst>
 </file>
@@ -2300,27 +2303,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14" t="str">
+    <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="12">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="13">
+        <v>350</v>
+      </c>
+      <c r="C32" s="13">
+        <v>0</v>
+      </c>
+      <c r="D32" s="13">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13">
+        <v>100</v>
+      </c>
+      <c r="F32" s="13">
+        <v>150</v>
+      </c>
+      <c r="G32" s="13">
+        <v>3</v>
+      </c>
+      <c r="H32" s="13">
+        <v>200</v>
+      </c>
+      <c r="I32" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J32" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D00F7AD-CA3F-CA4B-B426-8E9392C99361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CF2DB3-6642-684D-AE22-2DFAEFFF4C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>CA of CAP7001</t>
+  </si>
+  <si>
+    <t>Second RPL got rejected, Edu Rev is just a big joke.</t>
   </si>
 </sst>
 </file>
@@ -2349,27 +2352,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14" t="str">
+    <row r="33" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="13">
+        <v>300</v>
+      </c>
+      <c r="C33" s="13">
+        <v>0</v>
+      </c>
+      <c r="D33" s="13">
+        <v>0</v>
+      </c>
+      <c r="E33" s="13">
+        <v>90</v>
+      </c>
+      <c r="F33" s="13">
+        <v>350</v>
+      </c>
+      <c r="G33" s="13">
+        <v>7</v>
+      </c>
+      <c r="H33" s="13">
+        <v>200</v>
+      </c>
+      <c r="I33" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="14" t="str">
+        <v>940</v>
+      </c>
+      <c r="J33" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CF2DB3-6642-684D-AE22-2DFAEFFF4C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178EC445-3D57-A54F-A1D2-F5B69C1C89A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2398,27 +2398,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14" t="str">
+    <row r="34" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="13">
+        <v>410</v>
+      </c>
+      <c r="C34" s="13">
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13">
+        <v>60</v>
+      </c>
+      <c r="F34" s="13">
+        <v>200</v>
+      </c>
+      <c r="G34" s="13">
+        <v>4</v>
+      </c>
+      <c r="H34" s="13">
+        <v>200</v>
+      </c>
+      <c r="I34" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J34" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178EC445-3D57-A54F-A1D2-F5B69C1C89A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53198B62-7001-C94D-B911-C8EE42B219BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Second RPL got rejected, Edu Rev is just a big joke.</t>
+  </si>
+  <si>
+    <t>Celeberated Freshers as well friends birthday.</t>
   </si>
 </sst>
 </file>
@@ -2444,27 +2447,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14" t="str">
+    <row r="35" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A35" s="12">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="13">
+        <v>250</v>
+      </c>
+      <c r="C35" s="13">
+        <v>0</v>
+      </c>
+      <c r="D35" s="13">
+        <v>70</v>
+      </c>
+      <c r="E35" s="13">
+        <v>30</v>
+      </c>
+      <c r="F35" s="13">
+        <v>150</v>
+      </c>
+      <c r="G35" s="13">
+        <v>3</v>
+      </c>
+      <c r="H35" s="13">
+        <v>200</v>
+      </c>
+      <c r="I35" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="14" t="str">
+        <v>700</v>
+      </c>
+      <c r="J35" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="16"/>
+        <v>740</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53198B62-7001-C94D-B911-C8EE42B219BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A24EF2-58C6-034A-80C9-C55CA75474FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>Celeberated Freshers as well friends birthday.</t>
+  </si>
+  <si>
+    <t>Gave CA of Database.</t>
   </si>
 </sst>
 </file>
@@ -2493,27 +2496,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14" t="str">
+    <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="12">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="13">
+        <v>400</v>
+      </c>
+      <c r="C36" s="13">
+        <v>0</v>
+      </c>
+      <c r="D36" s="13">
+        <v>200</v>
+      </c>
+      <c r="E36" s="13">
+        <v>150</v>
+      </c>
+      <c r="F36" s="13">
+        <v>300</v>
+      </c>
+      <c r="G36" s="13">
+        <v>6</v>
+      </c>
+      <c r="H36" s="13">
+        <v>200</v>
+      </c>
+      <c r="I36" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="14" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J36" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="16" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A24EF2-58C6-034A-80C9-C55CA75474FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9485AF4-7645-234F-9913-6DDA8C90B569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Gave CA of Database.</t>
+  </si>
+  <si>
+    <t>Practicing for CA of Analytical Skills</t>
   </si>
 </sst>
 </file>
@@ -2542,27 +2545,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14" t="str">
+    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="12">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="13">
+        <v>420</v>
+      </c>
+      <c r="C37" s="13">
+        <v>0</v>
+      </c>
+      <c r="D37" s="13">
+        <v>200</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13">
+        <v>250</v>
+      </c>
+      <c r="I37" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J37" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9485AF4-7645-234F-9913-6DDA8C90B569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EC2430-FEA8-3E4A-B190-E53D9BC46EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2591,27 +2591,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="14" t="str">
+    <row r="38" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="12">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="13">
+        <v>400</v>
+      </c>
+      <c r="C38" s="13">
+        <v>0</v>
+      </c>
+      <c r="D38" s="13">
+        <v>150</v>
+      </c>
+      <c r="E38" s="13">
+        <v>300</v>
+      </c>
+      <c r="F38" s="13">
+        <v>0</v>
+      </c>
+      <c r="G38" s="13">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13">
+        <v>400</v>
+      </c>
+      <c r="I38" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J38" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EC2430-FEA8-3E4A-B190-E53D9BC46EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CDB388-18CD-1E47-9D79-29F7CD506615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>Practicing for CA of Analytical Skills</t>
+  </si>
+  <si>
+    <t>Solved DSA.</t>
   </si>
 </sst>
 </file>
@@ -2637,27 +2640,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14" t="str">
+    <row r="39" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="12">
+        <v>46279</v>
+      </c>
+      <c r="B39" s="13">
+        <v>400</v>
+      </c>
+      <c r="C39" s="13">
+        <v>0</v>
+      </c>
+      <c r="D39" s="13">
+        <v>90</v>
+      </c>
+      <c r="E39" s="13">
+        <v>350</v>
+      </c>
+      <c r="F39" s="13">
+        <v>150</v>
+      </c>
+      <c r="G39" s="13">
+        <v>3</v>
+      </c>
+      <c r="H39" s="13">
+        <v>250</v>
+      </c>
+      <c r="I39" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="14" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J39" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CDB388-18CD-1E47-9D79-29F7CD506615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312B08E3-184D-8047-82F9-A8A3990DC5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>Solved DSA.</t>
+  </si>
+  <si>
+    <t>Solved DSA and Gave Python CA.</t>
   </si>
 </sst>
 </file>
@@ -2686,27 +2689,51 @@
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14" t="str">
+    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B40" s="13">
+        <v>400</v>
+      </c>
+      <c r="C40" s="13">
+        <v>0</v>
+      </c>
+      <c r="D40" s="13">
+        <v>200</v>
+      </c>
+      <c r="E40" s="13">
+        <v>300</v>
+      </c>
+      <c r="F40" s="13">
+        <v>250</v>
+      </c>
+      <c r="G40" s="13">
+        <v>5</v>
+      </c>
+      <c r="H40" s="13">
+        <v>200</v>
+      </c>
+      <c r="I40" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="14" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J40" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312B08E3-184D-8047-82F9-A8A3990DC5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B8E332-464D-8A42-863C-24B6E9F808FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>Solved DSA and Gave Python CA.</t>
+  </si>
+  <si>
+    <t>Solved DSA and Prepared for Analytical Skill CA.</t>
   </si>
 </sst>
 </file>
@@ -2735,27 +2738,51 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14" t="str">
+    <row r="41" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A41" s="12">
+        <v>46281</v>
+      </c>
+      <c r="B41" s="13">
+        <v>400</v>
+      </c>
+      <c r="C41" s="13">
+        <v>0</v>
+      </c>
+      <c r="D41" s="13">
+        <v>300</v>
+      </c>
+      <c r="E41" s="13">
+        <v>150</v>
+      </c>
+      <c r="F41" s="13">
+        <v>150</v>
+      </c>
+      <c r="G41" s="13">
+        <v>3</v>
+      </c>
+      <c r="H41" s="13">
+        <v>200</v>
+      </c>
+      <c r="I41" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="14" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J41" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B8E332-464D-8A42-863C-24B6E9F808FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91849201-E089-034D-AC19-AEDC7C2B7E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2784,27 +2784,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14" t="str">
+    <row r="42" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A42" s="12">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="13">
+        <v>380</v>
+      </c>
+      <c r="C42" s="13">
+        <v>0</v>
+      </c>
+      <c r="D42" s="13">
+        <v>350</v>
+      </c>
+      <c r="E42" s="13">
+        <v>100</v>
+      </c>
+      <c r="F42" s="13">
+        <v>350</v>
+      </c>
+      <c r="G42" s="13">
+        <v>7</v>
+      </c>
+      <c r="H42" s="13">
+        <v>200</v>
+      </c>
+      <c r="I42" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="14" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J42" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N42" s="16" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91849201-E089-034D-AC19-AEDC7C2B7E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73671133-0B41-F24C-B057-2C42CCA0C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Solved DSA and Prepared for Analytical Skill CA.</t>
+  </si>
+  <si>
+    <t>Had Second Mentor Meeting.</t>
   </si>
 </sst>
 </file>
@@ -2830,27 +2833,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14" t="str">
+    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="12">
+        <v>46283</v>
+      </c>
+      <c r="B43" s="13">
+        <v>410</v>
+      </c>
+      <c r="C43" s="13">
+        <v>0</v>
+      </c>
+      <c r="D43" s="13">
+        <v>300</v>
+      </c>
+      <c r="E43" s="13">
+        <v>100</v>
+      </c>
+      <c r="F43" s="13">
+        <v>300</v>
+      </c>
+      <c r="G43" s="13">
+        <v>6</v>
+      </c>
+      <c r="H43" s="13">
+        <v>200</v>
+      </c>
+      <c r="I43" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="14" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73671133-0B41-F24C-B057-2C42CCA0C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B3E89A-0C80-C847-BCC1-0A8050474CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Had Second Mentor Meeting.</t>
+  </si>
+  <si>
+    <t>Gave CA of Analytical Skill</t>
   </si>
 </sst>
 </file>
@@ -2879,27 +2882,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14" t="str">
+    <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B44" s="13">
+        <v>350</v>
+      </c>
+      <c r="C44" s="13">
+        <v>0</v>
+      </c>
+      <c r="D44" s="13">
+        <v>0</v>
+      </c>
+      <c r="E44" s="13">
+        <v>300</v>
+      </c>
+      <c r="F44" s="13">
+        <v>100</v>
+      </c>
+      <c r="G44" s="13">
+        <v>2</v>
+      </c>
+      <c r="H44" s="13">
+        <v>240</v>
+      </c>
+      <c r="I44" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="str">
+        <v>990</v>
+      </c>
+      <c r="J44" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B3E89A-0C80-C847-BCC1-0A8050474CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1312A81-A299-F34C-9C12-82DB2BBB92C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>Gave CA of Analytical Skill</t>
+  </si>
+  <si>
+    <t>Solved DSA and wrote some code for Minor Project of Python.</t>
   </si>
 </sst>
 </file>
@@ -2928,27 +2931,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="str">
+    <row r="45" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A45" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="13">
+        <v>450</v>
+      </c>
+      <c r="C45" s="13">
+        <v>0</v>
+      </c>
+      <c r="D45" s="13">
+        <v>60</v>
+      </c>
+      <c r="E45" s="13">
+        <v>450</v>
+      </c>
+      <c r="F45" s="13">
+        <v>0</v>
+      </c>
+      <c r="G45" s="13">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13">
+        <v>200</v>
+      </c>
+      <c r="I45" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="14" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J45" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1312A81-A299-F34C-9C12-82DB2BBB92C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43883EA7-39C5-8D42-9F98-70E436009539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>Solved DSA and wrote some code for Minor Project of Python.</t>
+  </si>
+  <si>
+    <t>Learned Kadane's Algorithm and Completed Minor Project of Python.</t>
   </si>
 </sst>
 </file>
@@ -2977,27 +2980,51 @@
         <v>97</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14" t="str">
+    <row r="46" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+      <c r="A46" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="13">
+        <v>400</v>
+      </c>
+      <c r="C46" s="13">
+        <v>0</v>
+      </c>
+      <c r="D46" s="13">
+        <v>120</v>
+      </c>
+      <c r="E46" s="13">
+        <v>450</v>
+      </c>
+      <c r="F46" s="13">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13">
+        <v>240</v>
+      </c>
+      <c r="I46" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J46" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
@@ -10792,7 +10819,6 @@
       <c r="B401" s="13"/>
       <c r="C401" s="13"/>
       <c r="D401" s="13"/>
-      <c r="E401" s="13"/>
       <c r="F401" s="13"/>
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43883EA7-39C5-8D42-9F98-70E436009539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C5F368-2EF9-4649-AC98-CBEE06BE4E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3026,27 +3026,51 @@
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14" t="str">
+    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B47" s="13">
+        <v>400</v>
+      </c>
+      <c r="C47" s="13">
+        <v>0</v>
+      </c>
+      <c r="D47" s="13">
+        <v>250</v>
+      </c>
+      <c r="E47" s="13">
+        <v>200</v>
+      </c>
+      <c r="F47" s="13">
+        <v>350</v>
+      </c>
+      <c r="G47" s="13">
+        <v>7</v>
+      </c>
+      <c r="H47" s="13">
+        <v>200</v>
+      </c>
+      <c r="I47" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J47" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M47" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C5F368-2EF9-4649-AC98-CBEE06BE4E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F2A447-7D23-8D4D-B68D-E6D6EF375724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3072,27 +3072,51 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14" t="str">
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="12">
+        <v>46291</v>
+      </c>
+      <c r="B48" s="13">
+        <v>450</v>
+      </c>
+      <c r="C48" s="13">
+        <v>0</v>
+      </c>
+      <c r="D48" s="13">
+        <v>200</v>
+      </c>
+      <c r="E48" s="13">
+        <v>60</v>
+      </c>
+      <c r="F48" s="13">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
+        <v>500</v>
+      </c>
+      <c r="I48" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J48" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F2A447-7D23-8D4D-B68D-E6D6EF375724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5CF219-4375-8B4A-B796-F7FE744C2450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Learned Kadane's Algorithm and Completed Minor Project of Python.</t>
+  </si>
+  <si>
+    <t>Solved Analytical Exercise on HitBullsEye.</t>
   </si>
 </sst>
 </file>
@@ -3118,27 +3121,51 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14" t="str">
+    <row r="49" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A49" s="12">
+        <v>46306</v>
+      </c>
+      <c r="B49" s="13">
+        <v>460</v>
+      </c>
+      <c r="C49" s="13">
+        <v>0</v>
+      </c>
+      <c r="D49" s="13">
+        <v>400</v>
+      </c>
+      <c r="E49" s="13">
+        <v>60</v>
+      </c>
+      <c r="F49" s="13">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
+        <v>400</v>
+      </c>
+      <c r="I49" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="14" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J49" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5CF219-4375-8B4A-B796-F7FE744C2450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DF1A98-69C6-B245-9220-13BF6CEFC9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3167,27 +3167,51 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14" t="str">
+    <row r="50" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A50" s="12">
+        <v>46309</v>
+      </c>
+      <c r="B50" s="13">
+        <v>420</v>
+      </c>
+      <c r="C50" s="13">
+        <v>90</v>
+      </c>
+      <c r="D50" s="13">
+        <v>430</v>
+      </c>
+      <c r="E50" s="13">
+        <v>100</v>
+      </c>
+      <c r="F50" s="13">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13">
+        <v>350</v>
+      </c>
+      <c r="I50" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J50" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M50" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CAE466-4067-7940-9A71-BC604221B4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5890EA65-A345-C945-9B54-2ADD556300D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3309,27 +3309,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="14"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="16" t="str">
+    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A53" s="19">
+        <v>46317</v>
+      </c>
+      <c r="B53" s="15">
+        <v>370</v>
+      </c>
+      <c r="C53" s="15">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15">
+        <v>0</v>
+      </c>
+      <c r="E53" s="15">
+        <v>110</v>
+      </c>
+      <c r="F53" s="15">
+        <v>350</v>
+      </c>
+      <c r="G53" s="15">
+        <v>7</v>
+      </c>
+      <c r="H53" s="15">
+        <v>350</v>
+      </c>
+      <c r="I53" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="16" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J53" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="18"/>
+        <v>260</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="M53" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N53" s="18" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="14"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5890EA65-A345-C945-9B54-2ADD556300D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F8A750-F2D2-1D46-AE94-44829A3CDFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Feeling Weak and Disy due to fever.</t>
+  </si>
+  <si>
+    <t>Trying to build Consistency.</t>
   </si>
 </sst>
 </file>
@@ -3356,26 +3359,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="14"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="16" t="str">
+      <c r="A54" s="19">
+        <v>46319</v>
+      </c>
+      <c r="B54" s="15">
+        <v>440</v>
+      </c>
+      <c r="C54" s="15">
+        <v>90</v>
+      </c>
+      <c r="D54" s="15">
+        <v>120</v>
+      </c>
+      <c r="E54" s="15">
+        <v>60</v>
+      </c>
+      <c r="F54" s="15">
+        <v>0</v>
+      </c>
+      <c r="G54" s="15">
+        <v>0</v>
+      </c>
+      <c r="H54" s="15">
+        <v>350</v>
+      </c>
+      <c r="I54" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="16" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J54" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="18"/>
+        <v>380</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L54" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="N54" s="18" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="14"/>
